--- a/data/2025/16-dambovita/65342-targoviste/budget_file.xlsx
+++ b/data/2025/16-dambovita/65342-targoviste/budget_file.xlsx
@@ -35113,7 +35113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -35135,7 +35135,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -35145,60 +35145,230 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>611</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>611</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4888</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4888</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>69c1154f1a7941f1ae3ec36f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>c4a9f22e039db03e67678f16d82886c5daa175d5e3f14a3b08ae58be87536327</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL DETALIAT LA VENITURI PE CAPITOLE SI SUBCAPITOL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-22, 622 linii</t>
         </is>
